--- a/product_selector_out/STM32H5 series.xlsx
+++ b/product_selector_out/STM32H5 series.xlsx
@@ -11111,7 +11111,7 @@
       </c>
       <c r="BO41" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="BO42" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="BO43" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="BO45" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -12796,7 +12796,7 @@
       </c>
       <c r="BO46" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="BO47" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="BO48" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -13807,7 +13807,7 @@
       </c>
       <c r="BO49" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -14818,7 +14818,7 @@
       </c>
       <c r="BO52" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -25939,7 +25939,7 @@
       </c>
       <c r="BO85" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -26276,7 +26276,7 @@
       </c>
       <c r="BO86" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -26613,7 +26613,7 @@
       </c>
       <c r="BO87" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -26950,7 +26950,7 @@
       </c>
       <c r="BO88" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="BO89" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -27624,7 +27624,7 @@
       </c>
       <c r="BO90" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -27961,7 +27961,7 @@
       </c>
       <c r="BO91" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -28298,7 +28298,7 @@
       </c>
       <c r="BO92" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -28635,7 +28635,7 @@
       </c>
       <c r="BO93" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -28972,7 +28972,7 @@
       </c>
       <c r="BO94" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -29309,7 +29309,7 @@
       </c>
       <c r="BO95" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -29646,7 +29646,7 @@
       </c>
       <c r="BO96" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -30574,9 +30574,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY12" s="6" t="inlineStr">
@@ -30911,9 +30911,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY13" s="6" t="inlineStr">
@@ -31248,9 +31248,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY14" s="6" t="inlineStr">
@@ -31585,9 +31585,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY15" s="6" t="inlineStr">
@@ -31922,9 +31922,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY16" s="6" t="inlineStr">
@@ -32259,9 +32259,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY17" s="6" t="inlineStr">
@@ -32596,9 +32596,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY18" s="6" t="inlineStr">
@@ -32933,9 +32933,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY19" s="6" t="inlineStr">
@@ -33270,9 +33270,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY20" s="6" t="inlineStr">
@@ -33607,9 +33607,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY21" s="6" t="inlineStr">
@@ -33944,9 +33944,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY22" s="6" t="inlineStr">
@@ -34281,9 +34281,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY23" s="6" t="inlineStr">
@@ -34618,9 +34618,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY24" s="6" t="inlineStr">
@@ -34955,9 +34955,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX25" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY25" s="6" t="inlineStr">
@@ -35292,9 +35292,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY26" s="6" t="inlineStr">
@@ -35629,9 +35629,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY27" s="6" t="inlineStr">
@@ -35966,9 +35966,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX28" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY28" s="6" t="inlineStr">
@@ -36303,9 +36303,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX29" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY29" s="6" t="inlineStr">
@@ -36640,9 +36640,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX30" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY30" s="6" t="inlineStr">
@@ -36977,9 +36977,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX31" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY31" s="6" t="inlineStr">
@@ -37314,9 +37314,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX32" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY32" s="6" t="inlineStr">
@@ -37651,9 +37651,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX33" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX33" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY33" s="6" t="inlineStr">
@@ -37988,9 +37988,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX34" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX34" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY34" s="6" t="inlineStr">
@@ -38325,9 +38325,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX35" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX35" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY35" s="6" t="inlineStr">
@@ -38662,9 +38662,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX36" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX36" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY36" s="6" t="inlineStr">
@@ -38999,9 +38999,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX37" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX37" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY37" s="6" t="inlineStr">
@@ -39336,9 +39336,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX38" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX38" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY38" s="6" t="inlineStr">
@@ -39673,9 +39673,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX39" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX39" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY39" s="6" t="inlineStr">
@@ -40010,9 +40010,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX40" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX40" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY40" s="6" t="inlineStr">
@@ -40122,9 +40122,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -40342,14 +40342,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW41" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX41" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY41" s="6" t="inlineStr">
@@ -40432,9 +40432,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -40459,9 +40459,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -40679,14 +40679,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW42" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX42" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY42" s="6" t="inlineStr">
@@ -40769,9 +40769,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO42" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -40796,9 +40796,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -41016,14 +41016,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW43" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX43" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY43" s="6" t="inlineStr">
@@ -41106,9 +41106,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO43" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -41358,9 +41358,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX44" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX44" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY44" s="6" t="inlineStr">
@@ -41470,9 +41470,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
@@ -41690,14 +41690,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW45" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX45" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY45" s="6" t="inlineStr">
@@ -41780,9 +41780,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO45" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -41807,9 +41807,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -42027,14 +42027,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW46" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX46" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY46" s="6" t="inlineStr">
@@ -42117,9 +42117,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO46" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -42144,9 +42144,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
@@ -42364,14 +42364,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW47" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX47" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW47" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX47" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY47" s="6" t="inlineStr">
@@ -42454,9 +42454,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO47" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -42481,9 +42481,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
@@ -42701,14 +42701,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW48" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX48" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW48" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX48" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY48" s="6" t="inlineStr">
@@ -42791,9 +42791,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO48" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO48" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -42818,9 +42818,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
@@ -43038,14 +43038,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW49" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX49" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW49" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX49" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY49" s="6" t="inlineStr">
@@ -43128,9 +43128,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO49" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO49" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -43380,9 +43380,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX50" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX50" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY50" s="6" t="inlineStr">
@@ -43717,9 +43717,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX51" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX51" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY51" s="6" t="inlineStr">
@@ -43829,9 +43829,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
@@ -44049,14 +44049,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW52" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX52" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW52" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX52" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY52" s="6" t="inlineStr">
@@ -44139,9 +44139,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO52" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO52" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -44391,9 +44391,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX53" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX53" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY53" s="9" t="inlineStr">
@@ -44728,9 +44728,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX54" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX54" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY54" s="9" t="inlineStr">
@@ -45065,9 +45065,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX55" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX55" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY55" s="9" t="inlineStr">
@@ -45402,9 +45402,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX56" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX56" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY56" s="9" t="inlineStr">
@@ -45739,9 +45739,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX57" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX57" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY57" s="6" t="inlineStr">
@@ -46076,9 +46076,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX58" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX58" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY58" s="6" t="inlineStr">
@@ -46413,9 +46413,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX59" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX59" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY59" s="6" t="inlineStr">
@@ -46750,9 +46750,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX60" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX60" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY60" s="6" t="inlineStr">
@@ -47087,9 +47087,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX61" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX61" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY61" s="6" t="inlineStr">
@@ -47424,9 +47424,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX62" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX62" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY62" s="6" t="inlineStr">
@@ -47761,9 +47761,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX63" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX63" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY63" s="6" t="inlineStr">
@@ -48098,9 +48098,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX64" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX64" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY64" s="6" t="inlineStr">
@@ -48435,9 +48435,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX65" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX65" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY65" s="6" t="inlineStr">
@@ -48772,9 +48772,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX66" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX66" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY66" s="6" t="inlineStr">
@@ -49109,9 +49109,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX67" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX67" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY67" s="6" t="inlineStr">
@@ -49446,9 +49446,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX68" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX68" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY68" s="6" t="inlineStr">
@@ -49783,9 +49783,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX69" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX69" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY69" s="6" t="inlineStr">
@@ -50120,9 +50120,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX70" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX70" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY70" s="6" t="inlineStr">
@@ -50457,9 +50457,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX71" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX71" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY71" s="6" t="inlineStr">
@@ -50794,9 +50794,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX72" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX72" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY72" s="6" t="inlineStr">
@@ -51131,9 +51131,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX73" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX73" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY73" s="6" t="inlineStr">
@@ -51468,9 +51468,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX74" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX74" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY74" s="6" t="inlineStr">
@@ -51805,9 +51805,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX75" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX75" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY75" s="6" t="inlineStr">
@@ -52142,9 +52142,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX76" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX76" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY76" s="6" t="inlineStr">
@@ -52479,9 +52479,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX77" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX77" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY77" s="6" t="inlineStr">
@@ -52816,9 +52816,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX78" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX78" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY78" s="6" t="inlineStr">
@@ -53153,9 +53153,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX79" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX79" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY79" s="6" t="inlineStr">
@@ -53490,9 +53490,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX80" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX80" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY80" s="6" t="inlineStr">
@@ -53827,9 +53827,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX81" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX81" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY81" s="6" t="inlineStr">
@@ -54164,9 +54164,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX82" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX82" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY82" s="6" t="inlineStr">
@@ -54501,9 +54501,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX83" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX83" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY83" s="6" t="inlineStr">
@@ -54838,9 +54838,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX84" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX84" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY84" s="6" t="inlineStr">
@@ -54950,9 +54950,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E85" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
@@ -55170,14 +55170,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW85" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX85" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW85" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX85" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY85" s="6" t="inlineStr">
@@ -55260,9 +55260,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO85" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO85" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -55287,9 +55287,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
@@ -55507,14 +55507,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW86" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX86" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY86" s="6" t="inlineStr">
@@ -55597,9 +55597,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO86" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -55624,9 +55624,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
@@ -55844,14 +55844,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW87" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX87" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY87" s="6" t="inlineStr">
@@ -55934,9 +55934,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO87" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO87" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -55961,9 +55961,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
@@ -56181,14 +56181,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW88" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX88" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW88" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX88" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY88" s="6" t="inlineStr">
@@ -56271,9 +56271,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO88" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO88" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -56298,9 +56298,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
@@ -56518,14 +56518,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW89" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX89" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW89" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX89" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY89" s="6" t="inlineStr">
@@ -56608,9 +56608,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO89" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO89" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -56635,9 +56635,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr">
@@ -56855,14 +56855,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW90" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX90" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW90" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX90" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY90" s="6" t="inlineStr">
@@ -56945,9 +56945,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO90" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO90" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -56972,9 +56972,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E91" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
@@ -57192,14 +57192,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW91" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX91" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW91" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX91" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY91" s="6" t="inlineStr">
@@ -57282,9 +57282,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO91" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO91" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -57309,9 +57309,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E92" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
@@ -57529,14 +57529,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW92" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX92" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW92" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX92" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY92" s="6" t="inlineStr">
@@ -57619,9 +57619,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO92" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO92" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -57646,9 +57646,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
@@ -57866,14 +57866,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW93" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX93" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW93" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX93" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY93" s="6" t="inlineStr">
@@ -57956,9 +57956,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO93" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO93" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -57983,9 +57983,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr">
@@ -58203,14 +58203,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW94" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX94" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW94" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX94" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY94" s="6" t="inlineStr">
@@ -58293,9 +58293,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO94" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO94" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -58320,9 +58320,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E95" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
@@ -58540,14 +58540,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW95" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX95" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW95" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX95" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY95" s="6" t="inlineStr">
@@ -58630,9 +58630,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO95" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO95" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -58657,9 +58657,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E96" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr">
@@ -58877,14 +58877,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW96" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX96" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW96" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX96" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY96" s="6" t="inlineStr">
@@ -58967,9 +58967,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO96" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO96" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -58988,7 +58988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D116"/>
+  <dimension ref="A1:D159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -59037,19 +59037,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32H563IG</t>
+          <t>STM32H563LI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -59059,14 +59059,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32H563ZI</t>
+          <t>STM32H563IG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -59081,19 +59081,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32H573MI</t>
+          <t>STM32H563IG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -59103,14 +59103,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32H573RI</t>
+          <t>STM32H563ZI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -59125,19 +59125,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32H563MI</t>
+          <t>STM32H563ZI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -59147,14 +59147,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32H563RG</t>
+          <t>STM32H573MI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -59169,19 +59169,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32H573ZI</t>
+          <t>STM32H573MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -59191,14 +59191,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32H563ZG</t>
+          <t>STM32H573RI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -59213,19 +59213,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32H573II</t>
+          <t>STM32H573RI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -59235,14 +59235,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32H563VG</t>
+          <t>STM32H563MI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -59257,19 +59257,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32H573VI</t>
+          <t>STM32H563MI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -59279,14 +59279,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32H563RI</t>
+          <t>STM32H563RG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -59301,19 +59301,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32H563VI</t>
+          <t>STM32H563RG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -59323,14 +59323,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32H573AI</t>
+          <t>STM32H573ZI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -59345,19 +59345,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32H563AI</t>
+          <t>STM32H573ZI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -59367,14 +59367,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32H563II</t>
+          <t>STM32H563ZG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -59389,19 +59389,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32H563AG</t>
+          <t>STM32H563ZG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -59411,14 +59411,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32H573LI</t>
+          <t>STM32H573II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -59433,19 +59433,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32H562AG</t>
+          <t>STM32H573II</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -59455,14 +59455,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32H562IG</t>
+          <t>STM32H563VG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -59477,19 +59477,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32H562VI</t>
+          <t>STM32H563VG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -59499,14 +59499,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32H562ZI</t>
+          <t>STM32H573VI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -59521,19 +59521,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32H562ZG</t>
+          <t>STM32H573VI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -59543,14 +59543,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32H562VG</t>
+          <t>STM32H563RI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -59565,19 +59565,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32H562RG</t>
+          <t>STM32H563RI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -59587,14 +59587,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32H562RI</t>
+          <t>STM32H563VI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -59609,19 +59609,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32H562AI</t>
+          <t>STM32H563VI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -59631,14 +59631,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32H562II</t>
+          <t>STM32H573AI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -59653,19 +59653,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32H5E4AK</t>
+          <t>STM32H573AI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -59675,14 +59675,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32H5E4IK</t>
+          <t>STM32H563AI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -59697,19 +59697,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32H5E4VK</t>
+          <t>STM32H563AI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -59719,14 +59719,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32H5E4VJ</t>
+          <t>STM32H563II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -59741,19 +59741,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32H5E4ZJ</t>
+          <t>STM32H563II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -59763,14 +59763,14 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32H5F4IJ</t>
+          <t>STM32H563AG</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -59785,19 +59785,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32H5E4ZK</t>
+          <t>STM32H563AG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -59807,14 +59807,14 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32H5F4VJ</t>
+          <t>STM32H573LI</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -59829,19 +59829,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32H5F4ZJ</t>
+          <t>STM32H573LI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -59851,14 +59851,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32H5E4AJ</t>
+          <t>STM32H562AG</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -59873,19 +59873,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32H5F4AJ</t>
+          <t>STM32H562AG</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -59895,14 +59895,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32H5E4IJ</t>
+          <t>STM32H562IG</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -59917,19 +59917,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32H503EB</t>
+          <t>STM32H562IG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -59939,19 +59939,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32H503EB</t>
+          <t>STM32H562VI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -59961,19 +59961,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32H503EB</t>
+          <t>STM32H562VI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -59983,19 +59983,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32H503EB</t>
+          <t>STM32H562ZI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -60005,19 +60005,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Table 33. Peripheral current consumption in Sleep mode</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32H503KB</t>
+          <t>STM32H562ZI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -60027,19 +60027,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32H503KB</t>
+          <t>STM32H562ZG</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -60049,19 +60049,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32H503KB</t>
+          <t>STM32H562ZG</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -60071,19 +60071,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32H503KB</t>
+          <t>STM32H562VG</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -60093,19 +60093,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Table 33. Peripheral current consumption in Sleep mode</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32H503CB</t>
+          <t>STM32H562VG</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -60115,19 +60115,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32H503CB</t>
+          <t>STM32H562RG</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -60137,19 +60137,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32H503CB</t>
+          <t>STM32H562RG</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -60159,19 +60159,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32H503CB</t>
+          <t>STM32H562RI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -60181,19 +60181,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Table 33. Peripheral current consumption in Sleep mode</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32H503RB</t>
+          <t>STM32H562RI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -60203,19 +60203,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32H503RB</t>
+          <t>STM32H562AI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -60225,19 +60225,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32H503RB</t>
+          <t>STM32H562AI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -60247,19 +60247,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32H503RB</t>
+          <t>STM32H562II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -60269,19 +60269,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 33. Peripheral current consumption in Sleep mode</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32H553UG</t>
+          <t>STM32H562II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -60291,14 +60291,14 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32H543CE</t>
+          <t>STM32H5E4VJ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -60313,19 +60313,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32H543RG</t>
+          <t>STM32H5E4VJ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -60335,14 +60335,14 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32H553CG</t>
+          <t>STM32H5E4AJ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -60357,19 +60357,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32H543CG</t>
+          <t>STM32H5E4AJ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -60379,14 +60379,14 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32H543VG</t>
+          <t>STM32H5F4AJ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -60401,19 +60401,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32H553ZG</t>
+          <t>STM32H5F4AJ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -60423,19 +60423,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32H543VE</t>
+          <t>STM32H503EB</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -60445,19 +60445,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32H543UG</t>
+          <t>STM32H503EB</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -60467,14 +60467,14 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32H543RE</t>
+          <t>STM32H503EB</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -60489,19 +60489,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32H553RG</t>
+          <t>STM32H503EB</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -60511,19 +60511,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32H553VG</t>
+          <t>STM32H503EB</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -60533,19 +60533,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 33. Peripheral current consumption in Sleep mode</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32H543ZG</t>
+          <t>STM32H503KB</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -60555,19 +60555,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32H543ZE</t>
+          <t>STM32H503KB</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -60577,19 +60577,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32H523CE</t>
+          <t>STM32H503KB</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -60599,19 +60599,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 16. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32H523CE</t>
+          <t>STM32H503KB</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -60621,19 +60621,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 16. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32H523CE</t>
+          <t>STM32H503KB</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -60643,19 +60643,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 33. Peripheral current consumption in Sleep mode</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32H523ZE</t>
+          <t>STM32H503CB</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -60665,19 +60665,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP144, UFBGA144 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32H523ZE</t>
+          <t>STM32H503CB</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -60687,14 +60687,14 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32H523ZE</t>
+          <t>STM32H503CB</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -60709,19 +60709,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H503CB</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -60731,19 +60731,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 16. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H503CB</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -60753,19 +60753,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 33. Peripheral current consumption in Sleep mode</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H503RB</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -60775,19 +60775,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H503RB</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -60797,19 +60797,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H503RB</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -60819,19 +60819,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 16. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H503RB</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -60841,19 +60841,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32H533VE</t>
+          <t>STM32H503RB</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -60863,19 +60863,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 33. Peripheral current consumption in Sleep mode</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H553UG</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -60885,19 +60885,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts lists WLCSP39 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H553UG</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -60907,14 +60907,14 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 18. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H543CE</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -60929,19 +60929,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32H533CE</t>
+          <t>STM32H543CE</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -60951,14 +60951,14 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32H533RE</t>
+          <t>STM32H543RG</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -60973,19 +60973,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32H533HE</t>
+          <t>STM32H543RG</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -60995,19 +60995,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H553CG</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -61017,19 +61017,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP144, UFBGA144 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H553CG</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -61039,14 +61039,14 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 18. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H543CG</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -61061,19 +61061,19 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H543CG</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -61083,19 +61083,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H543VG</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -61105,19 +61105,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H543VG</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -61127,19 +61127,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H553ZG</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -61149,19 +61149,19 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H553ZG</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -61171,14 +61171,14 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 18. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H543VE</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -61193,19 +61193,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H543VE</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -61215,19 +61215,19 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H543UG</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -61237,19 +61237,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H543UG</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -61259,14 +61259,14 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32H533ZE</t>
+          <t>STM32H543RE</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -61281,19 +61281,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32H5E5VK</t>
+          <t>STM32H543RE</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -61303,14 +61303,14 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32H5F5ZJ</t>
+          <t>STM32H553RG</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -61325,19 +61325,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32H5E5VJ</t>
+          <t>STM32H553RG</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -61347,14 +61347,14 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32H5E5ZK</t>
+          <t>STM32H553VG</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -61369,19 +61369,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32H5F5LJ</t>
+          <t>STM32H553VG</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -61391,14 +61391,14 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32H5F5IJ</t>
+          <t>STM32H543ZG</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -61413,19 +61413,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32H5E5LJ</t>
+          <t>STM32H543ZG</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -61435,14 +61435,14 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32H5E5ZJ</t>
+          <t>STM32H543ZE</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -61457,19 +61457,19 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32H5F5VJ</t>
+          <t>STM32H543ZE</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -61479,19 +61479,19 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32H5E5IJ</t>
+          <t>STM32H523CE</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -61501,19 +61501,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32H5E5IK</t>
+          <t>STM32H523CE</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -61523,14 +61523,14 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32H5E5LK</t>
+          <t>STM32H523CE</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -61545,7 +61545,953 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>STM32H523CE</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>STM32H523ZE</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP144, UFBGA144 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>STM32H523ZE</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>STM32H523ZE</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>STM32H523ZE</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>STM32H523RE</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>STM32H523RE</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>STM32H523RE</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>STM32H523RE</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>STM32H523VE</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>STM32H523VE</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>STM32H523VE</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>STM32H523VE</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>STM32H533VE</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>STM32H533VE</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>STM32H523HE</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Table 2. STM32H523xx features and peripheral counts lists WLCSP39 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>STM32H523HE</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>STM32H523HE</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>STM32H523HE</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>STM32H533CE</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>STM32H533CE</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>STM32H533RE</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>STM32H533RE</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>STM32H533HE</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>STM32H533HE</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>STM32H523ZC</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP144, UFBGA144 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>STM32H523ZC</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>STM32H523ZC</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>STM32H523ZC</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>STM32H523VC</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>STM32H523VC</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>STM32H523VC</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>STM32H523VC</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>STM32H533ZE</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>STM32H533ZE</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32H5 series.xlsx
+++ b/product_selector_out/STM32H5 series.xlsx
@@ -11111,7 +11111,7 @@
       </c>
       <c r="BO41" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="BO42" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
         </is>
       </c>
     </row>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="BO43" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="BO45" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
         </is>
       </c>
     </row>
@@ -12796,7 +12796,7 @@
       </c>
       <c r="BO46" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="BO47" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
         </is>
       </c>
     </row>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="BO48" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -13807,7 +13807,7 @@
       </c>
       <c r="BO49" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -14818,7 +14818,7 @@
       </c>
       <c r="BO52" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
         </is>
       </c>
     </row>
@@ -25939,7 +25939,7 @@
       </c>
       <c r="BO85" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
         </is>
       </c>
     </row>
@@ -26276,7 +26276,7 @@
       </c>
       <c r="BO86" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -26613,7 +26613,7 @@
       </c>
       <c r="BO87" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
         </is>
       </c>
     </row>
@@ -26950,7 +26950,7 @@
       </c>
       <c r="BO88" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
         </is>
       </c>
     </row>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="BO89" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -27624,7 +27624,7 @@
       </c>
       <c r="BO90" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -27961,7 +27961,7 @@
       </c>
       <c r="BO91" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
         </is>
       </c>
     </row>
@@ -28298,7 +28298,7 @@
       </c>
       <c r="BO92" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
         </is>
       </c>
     </row>
@@ -28635,7 +28635,7 @@
       </c>
       <c r="BO93" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -28972,7 +28972,7 @@
       </c>
       <c r="BO94" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
         </is>
       </c>
     </row>
@@ -29309,7 +29309,7 @@
       </c>
       <c r="BO95" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
         </is>
       </c>
     </row>
@@ -29646,7 +29646,7 @@
       </c>
       <c r="BO96" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
         </is>
       </c>
     </row>
@@ -40122,9 +40122,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -40342,14 +40342,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW41" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX41" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY41" s="6" t="inlineStr">
@@ -40432,9 +40432,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO41" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -40459,9 +40459,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -40679,14 +40679,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW42" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX42" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY42" s="6" t="inlineStr">
@@ -40769,9 +40769,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO42" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -40796,9 +40796,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -41016,14 +41016,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW43" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX43" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY43" s="6" t="inlineStr">
@@ -41106,9 +41106,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO43" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -41470,9 +41470,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
@@ -41690,14 +41690,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW45" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX45" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY45" s="6" t="inlineStr">
@@ -41780,9 +41780,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO45" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -41807,9 +41807,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -42027,14 +42027,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW46" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX46" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY46" s="6" t="inlineStr">
@@ -42117,9 +42117,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO46" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -42144,9 +42144,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
@@ -42364,14 +42364,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW47" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX47" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY47" s="6" t="inlineStr">
@@ -42454,9 +42454,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO47" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO47" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -42481,9 +42481,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
@@ -42701,14 +42701,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW48" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX48" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW48" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX48" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY48" s="6" t="inlineStr">
@@ -42791,9 +42791,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO48" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO48" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -42818,9 +42818,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
@@ -43038,14 +43038,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW49" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX49" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW49" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX49" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY49" s="6" t="inlineStr">
@@ -43128,9 +43128,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO49" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO49" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -43829,9 +43829,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
@@ -44049,14 +44049,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW52" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX52" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW52" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX52" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY52" s="6" t="inlineStr">
@@ -44139,9 +44139,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO52" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO52" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -54950,9 +54950,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E85" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
@@ -55170,14 +55170,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW85" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX85" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW85" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX85" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY85" s="6" t="inlineStr">
@@ -55260,9 +55260,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO85" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO85" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -55287,9 +55287,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
@@ -55507,14 +55507,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW86" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX86" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY86" s="6" t="inlineStr">
@@ -55597,9 +55597,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO86" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -55624,9 +55624,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
@@ -55844,14 +55844,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW87" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX87" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW87" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX87" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY87" s="6" t="inlineStr">
@@ -55934,9 +55934,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO87" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -55961,9 +55961,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E88" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
@@ -56181,14 +56181,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW88" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX88" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW88" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX88" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY88" s="6" t="inlineStr">
@@ -56271,9 +56271,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO88" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO88" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -56298,9 +56298,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
@@ -56518,14 +56518,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW89" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX89" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW89" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX89" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY89" s="6" t="inlineStr">
@@ -56608,9 +56608,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO89" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO89" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -56635,9 +56635,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E90" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr">
@@ -56855,14 +56855,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW90" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX90" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW90" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX90" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY90" s="6" t="inlineStr">
@@ -56945,9 +56945,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO90" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO90" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -56972,9 +56972,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E91" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
@@ -57192,14 +57192,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW91" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX91" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW91" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX91" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY91" s="6" t="inlineStr">
@@ -57282,9 +57282,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO91" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO91" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -57309,9 +57309,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E92" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
@@ -57529,14 +57529,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW92" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX92" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW92" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX92" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY92" s="6" t="inlineStr">
@@ -57619,9 +57619,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO92" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO92" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -57646,9 +57646,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E93" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
@@ -57866,14 +57866,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW93" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX93" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW93" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX93" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY93" s="6" t="inlineStr">
@@ -57956,9 +57956,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO93" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO93" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -57983,9 +57983,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E94" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr">
@@ -58203,14 +58203,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW94" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX94" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW94" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX94" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY94" s="6" t="inlineStr">
@@ -58293,9 +58293,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO94" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO94" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -58320,9 +58320,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
@@ -58540,14 +58540,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW95" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX95" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW95" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX95" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY95" s="6" t="inlineStr">
@@ -58630,9 +58630,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO95" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO95" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -58657,9 +58657,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E96" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr">
@@ -58877,14 +58877,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW96" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX96" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW96" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX96" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY96" s="6" t="inlineStr">
@@ -58967,9 +58967,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO96" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO96" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -58988,7 +58988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D159"/>
+  <dimension ref="A1:D201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -60298,7 +60298,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32H5E4VJ</t>
+          <t>STM32H5E4AK</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -60320,7 +60320,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32H5E4VJ</t>
+          <t>STM32H5E4AK</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -60342,7 +60342,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32H5E4AJ</t>
+          <t>STM32H5E4IK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -60364,7 +60364,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32H5E4AJ</t>
+          <t>STM32H5E4IK</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -60386,7 +60386,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32H5F4AJ</t>
+          <t>STM32H5E4VK</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -60401,14 +60401,14 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32H5F4AJ</t>
+          <t>STM32H5E4VK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -60423,19 +60423,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32H503EB</t>
+          <t>STM32H5E4VJ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -60445,19 +60445,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32H503EB</t>
+          <t>STM32H5E4VJ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -60467,14 +60467,14 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32H503EB</t>
+          <t>STM32H5E4ZJ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -60489,14 +60489,14 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32H503EB</t>
+          <t>STM32H5E4ZJ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -60511,19 +60511,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32H503EB</t>
+          <t>STM32H5F4IJ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -60533,19 +60533,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Table 33. Peripheral current consumption in Sleep mode</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32H503KB</t>
+          <t>STM32H5F4IJ</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -60555,19 +60555,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32H503KB</t>
+          <t>STM32H5E4ZK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -60577,19 +60577,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32H503KB</t>
+          <t>STM32H5E4ZK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -60599,19 +60599,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32H503KB</t>
+          <t>STM32H5F4VJ</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -60621,19 +60621,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32H503KB</t>
+          <t>STM32H5F4VJ</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -60643,19 +60643,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Table 33. Peripheral current consumption in Sleep mode</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32H503CB</t>
+          <t>STM32H5F4ZJ</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -60665,19 +60665,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32H503CB</t>
+          <t>STM32H5F4ZJ</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -60687,14 +60687,14 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32H503CB</t>
+          <t>STM32H5E4AJ</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -60709,14 +60709,14 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32H503CB</t>
+          <t>STM32H5E4AJ</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -60731,19 +60731,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32H503CB</t>
+          <t>STM32H5F4AJ</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -60753,19 +60753,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Table 33. Peripheral current consumption in Sleep mode</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32H503RB</t>
+          <t>STM32H5F4AJ</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -60775,19 +60775,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32H503RB</t>
+          <t>STM32H5E4IJ</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -60797,19 +60797,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32H503RB</t>
+          <t>STM32H5E4IJ</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -60819,19 +60819,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32H503RB</t>
+          <t>STM32H503EB</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -60841,19 +60841,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32H503RB</t>
+          <t>STM32H503EB</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -60863,14 +60863,14 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Table 33. Peripheral current consumption in Sleep mode</t>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32H553UG</t>
+          <t>STM32H503EB</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -60885,14 +60885,14 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 16. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32H553UG</t>
+          <t>STM32H503EB</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -60907,19 +60907,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 16. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32H543CE</t>
+          <t>STM32H503EB</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -60929,19 +60929,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 33. Peripheral current consumption in Sleep mode</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32H543CE</t>
+          <t>STM32H503KB</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -60951,19 +60951,19 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32H543RG</t>
+          <t>STM32H503KB</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -60973,19 +60973,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32H543RG</t>
+          <t>STM32H503KB</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -60995,19 +60995,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 16. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32H553CG</t>
+          <t>STM32H503KB</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -61017,19 +61017,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 16. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32H553CG</t>
+          <t>STM32H503KB</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -61039,19 +61039,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 33. Peripheral current consumption in Sleep mode</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32H543CG</t>
+          <t>STM32H503CB</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -61061,19 +61061,19 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32H543CG</t>
+          <t>STM32H503CB</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -61083,14 +61083,14 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32H543VG</t>
+          <t>STM32H503CB</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -61105,14 +61105,14 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 16. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32H543VG</t>
+          <t>STM32H503CB</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -61127,19 +61127,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 16. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32H553ZG</t>
+          <t>STM32H503CB</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -61149,19 +61149,19 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 33. Peripheral current consumption in Sleep mode</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32H553ZG</t>
+          <t>STM32H503RB</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -61171,19 +61171,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32H543VE</t>
+          <t>STM32H503RB</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -61193,19 +61193,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32H543VE</t>
+          <t>STM32H503RB</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -61215,19 +61215,19 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 16. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32H543UG</t>
+          <t>STM32H503RB</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -61237,19 +61237,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 16. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32H543UG</t>
+          <t>STM32H503RB</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -61259,14 +61259,14 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 33. Peripheral current consumption in Sleep mode</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32H543RE</t>
+          <t>STM32H553UG</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -61281,14 +61281,14 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32H543RE</t>
+          <t>STM32H553UG</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -61303,14 +61303,14 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 18. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32H553RG</t>
+          <t>STM32H543CE</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -61325,14 +61325,14 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32H553RG</t>
+          <t>STM32H543CE</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -61347,14 +61347,14 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32H553VG</t>
+          <t>STM32H543RG</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -61369,14 +61369,14 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32H553VG</t>
+          <t>STM32H543RG</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -61391,14 +61391,14 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32H543ZG</t>
+          <t>STM32H553CG</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -61413,14 +61413,14 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32H543ZG</t>
+          <t>STM32H553CG</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -61435,14 +61435,14 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 18. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32H543ZE</t>
+          <t>STM32H543CG</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -61464,7 +61464,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32H543ZE</t>
+          <t>STM32H543CG</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -61486,12 +61486,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32H523CE</t>
+          <t>STM32H543VG</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -61501,19 +61501,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32H523CE</t>
+          <t>STM32H543VG</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -61523,14 +61523,14 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32H523CE</t>
+          <t>STM32H553ZG</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -61545,14 +61545,14 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM32H523CE</t>
+          <t>STM32H553ZG</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -61567,19 +61567,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 18. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32H523ZE</t>
+          <t>STM32H543VE</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -61589,19 +61589,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP144, UFBGA144 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32H523ZE</t>
+          <t>STM32H543VE</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -61611,14 +61611,14 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32H523ZE</t>
+          <t>STM32H543UG</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -61633,14 +61633,14 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32H523ZE</t>
+          <t>STM32H543UG</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -61655,19 +61655,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H543RE</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -61677,19 +61677,19 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H543RE</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -61699,14 +61699,14 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H553RG</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -61721,14 +61721,14 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H553RG</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -61743,19 +61743,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 18. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H553VG</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -61765,19 +61765,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H553VG</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -61787,14 +61787,14 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 18. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H543ZG</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -61809,14 +61809,14 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H543ZG</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -61831,14 +61831,14 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>STM32H533VE</t>
+          <t>STM32H543ZE</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -61853,14 +61853,14 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>STM32H533VE</t>
+          <t>STM32H543ZE</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -61875,14 +61875,14 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523CE</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -61897,14 +61897,14 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts lists WLCSP39 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523CE</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -61926,7 +61926,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523CE</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -61948,7 +61948,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523CE</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -61970,12 +61970,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>STM32H533CE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -61985,19 +61985,19 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP144, UFBGA144 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>STM32H533CE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -62007,14 +62007,14 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>STM32H533RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -62029,14 +62029,14 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>STM32H533RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -62051,19 +62051,19 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>STM32H533HE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -62073,19 +62073,19 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>STM32H533HE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -62095,19 +62095,19 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -62117,19 +62117,19 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP144, UFBGA144 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -62139,19 +62139,19 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -62161,19 +62161,19 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -62183,19 +62183,19 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -62205,19 +62205,19 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -62227,14 +62227,14 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H533VE</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -62249,14 +62249,14 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H533VE</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -62271,14 +62271,14 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -62293,14 +62293,14 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32H523xx features and peripheral counts lists WLCSP39 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -62322,7 +62322,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -62344,7 +62344,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -62366,12 +62366,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H533CE</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -62381,19 +62381,19 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H533CE</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -62403,14 +62403,14 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H533RE</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -62425,14 +62425,14 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H533RE</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -62447,14 +62447,14 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>STM32H533ZE</t>
+          <t>STM32H533HE</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -62476,22 +62476,946 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
+          <t>STM32H533HE</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>STM32H523ZC</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP144, UFBGA144 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>STM32H523ZC</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>STM32H523ZC</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>STM32H523ZC</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>STM32H523VC</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>STM32H523VC</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>STM32H523VC</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>STM32H523VC</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
           <t>STM32H533ZE</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>STM32H533ZE</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
         <is>
           <t>Supply Voltage (V) max</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
+      <c r="C177" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
+      <c r="D177" t="inlineStr">
         <is>
           <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>STM32H5E5VK</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>STM32H5E5VK</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>STM32H5F5ZJ</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>STM32H5F5ZJ</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>STM32H5E5VJ</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>STM32H5E5VJ</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>STM32H5E5ZK</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>STM32H5E5ZK</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>STM32H5F5LJ</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>STM32H5F5LJ</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>STM32H5F5IJ</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>STM32H5F5IJ</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>STM32H5E5LJ</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>STM32H5E5LJ</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>STM32H5E5ZJ</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>STM32H5E5ZJ</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>STM32H5F5VJ</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>STM32H5F5VJ</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>STM32H5E5IJ</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>STM32H5E5IJ</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>STM32H5E5IK</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>STM32H5E5IK</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>STM32H5E5LK</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>STM32H5E5LK</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32H5 series.xlsx
+++ b/product_selector_out/STM32H5 series.xlsx
@@ -42,7 +42,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +74,11 @@
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -90,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
@@ -105,6 +110,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -20976,7 +20982,7 @@
       </c>
       <c r="R71" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S71" s="4" t="inlineStr">
@@ -21313,7 +21319,7 @@
       </c>
       <c r="R72" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S72" s="4" t="inlineStr">
@@ -21650,7 +21656,7 @@
       </c>
       <c r="R73" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S73" s="4" t="inlineStr">
@@ -21987,7 +21993,7 @@
       </c>
       <c r="R74" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S74" s="4" t="inlineStr">
@@ -22661,7 +22667,7 @@
       </c>
       <c r="R76" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S76" s="4" t="inlineStr">
@@ -24009,7 +24015,7 @@
       </c>
       <c r="R80" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S80" s="4" t="inlineStr">
@@ -24346,7 +24352,7 @@
       </c>
       <c r="R81" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S81" s="4" t="inlineStr">
@@ -24683,7 +24689,7 @@
       </c>
       <c r="R82" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S82" s="4" t="inlineStr">
@@ -25020,7 +25026,7 @@
       </c>
       <c r="R83" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S83" s="4" t="inlineStr">
@@ -50297,14 +50303,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R71" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S71" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T71" s="9" t="inlineStr">
@@ -50312,9 +50318,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U71" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V71" s="6" t="inlineStr">
@@ -50342,9 +50348,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA71" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB71" s="6" t="inlineStr">
@@ -50634,14 +50640,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R72" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S72" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T72" s="9" t="inlineStr">
@@ -50649,9 +50655,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U72" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V72" s="6" t="inlineStr">
@@ -50679,9 +50685,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA72" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB72" s="6" t="inlineStr">
@@ -50971,14 +50977,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R73" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S73" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R73" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S73" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T73" s="9" t="inlineStr">
@@ -50986,9 +50992,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U73" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U73" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V73" s="6" t="inlineStr">
@@ -51016,9 +51022,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA73" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA73" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB73" s="6" t="inlineStr">
@@ -51308,14 +51314,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R74" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S74" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R74" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S74" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T74" s="9" t="inlineStr">
@@ -51323,9 +51329,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U74" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U74" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V74" s="6" t="inlineStr">
@@ -51353,9 +51359,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA74" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA74" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB74" s="6" t="inlineStr">
@@ -51982,14 +51988,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R76" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S76" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R76" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S76" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T76" s="9" t="inlineStr">
@@ -51997,9 +52003,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U76" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U76" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V76" s="6" t="inlineStr">
@@ -52027,9 +52033,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA76" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA76" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB76" s="6" t="inlineStr">
@@ -53330,14 +53336,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R80" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S80" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R80" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S80" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T80" s="9" t="inlineStr">
@@ -53345,9 +53351,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U80" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U80" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V80" s="6" t="inlineStr">
@@ -53375,9 +53381,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA80" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA80" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB80" s="6" t="inlineStr">
@@ -53667,14 +53673,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R81" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S81" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R81" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S81" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T81" s="9" t="inlineStr">
@@ -53682,9 +53688,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U81" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U81" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V81" s="6" t="inlineStr">
@@ -53712,9 +53718,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA81" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA81" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB81" s="6" t="inlineStr">
@@ -54004,14 +54010,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R82" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S82" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R82" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S82" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T82" s="9" t="inlineStr">
@@ -54019,9 +54025,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U82" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U82" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V82" s="6" t="inlineStr">
@@ -54049,9 +54055,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA82" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA82" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB82" s="6" t="inlineStr">
@@ -54341,14 +54347,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R83" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S83" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R83" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S83" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T83" s="9" t="inlineStr">
@@ -54356,9 +54362,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U83" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U83" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V83" s="6" t="inlineStr">
@@ -54386,9 +54392,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA83" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA83" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB83" s="6" t="inlineStr">

--- a/product_selector_out/STM32H5 series.xlsx
+++ b/product_selector_out/STM32H5 series.xlsx
@@ -11117,7 +11117,7 @@
       </c>
       <c r="BO41" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -11454,7 +11454,7 @@
       </c>
       <c r="BO42" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -11791,7 +11791,7 @@
       </c>
       <c r="BO43" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -12128,7 +12128,7 @@
       </c>
       <c r="BO44" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -12465,7 +12465,7 @@
       </c>
       <c r="BO45" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -13139,7 +13139,7 @@
       </c>
       <c r="BO47" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -14824,7 +14824,7 @@
       </c>
       <c r="BO52" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -21087,7 +21087,7 @@
       </c>
       <c r="AM71" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN71" s="4" t="inlineStr">
@@ -21424,7 +21424,7 @@
       </c>
       <c r="AM72" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN72" s="4" t="inlineStr">
@@ -21761,7 +21761,7 @@
       </c>
       <c r="AM73" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN73" s="4" t="inlineStr">
@@ -22098,7 +22098,7 @@
       </c>
       <c r="AM74" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN74" s="4" t="inlineStr">
@@ -22772,7 +22772,7 @@
       </c>
       <c r="AM76" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN76" s="4" t="inlineStr">
@@ -24120,7 +24120,7 @@
       </c>
       <c r="AM80" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN80" s="4" t="inlineStr">
@@ -24457,7 +24457,7 @@
       </c>
       <c r="AM81" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN81" s="4" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="AM82" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN82" s="4" t="inlineStr">
@@ -25131,7 +25131,7 @@
       </c>
       <c r="AM83" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN83" s="4" t="inlineStr">
@@ -25945,7 +25945,7 @@
       </c>
       <c r="BO85" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -26619,7 +26619,7 @@
       </c>
       <c r="BO87" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -26956,7 +26956,7 @@
       </c>
       <c r="BO88" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -27967,7 +27967,7 @@
       </c>
       <c r="BO91" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -28304,7 +28304,7 @@
       </c>
       <c r="BO92" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -28978,7 +28978,7 @@
       </c>
       <c r="BO94" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -29315,7 +29315,7 @@
       </c>
       <c r="BO95" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -29652,7 +29652,7 @@
       </c>
       <c r="BO96" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h5e4vj.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
     </row>
@@ -50408,9 +50408,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM71" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN71" s="6" t="inlineStr">
@@ -50745,9 +50745,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM72" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN72" s="6" t="inlineStr">
@@ -51082,9 +51082,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM73" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM73" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN73" s="6" t="inlineStr">
@@ -51419,9 +51419,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM74" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM74" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN74" s="6" t="inlineStr">
@@ -52093,9 +52093,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM76" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM76" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN76" s="6" t="inlineStr">
@@ -53441,9 +53441,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM80" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM80" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN80" s="6" t="inlineStr">
@@ -53778,9 +53778,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM81" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM81" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN81" s="6" t="inlineStr">
@@ -54115,9 +54115,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM82" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM82" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN82" s="6" t="inlineStr">
@@ -54452,9 +54452,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM83" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM83" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN83" s="6" t="inlineStr">

--- a/product_selector_out/STM32H5 series.xlsx
+++ b/product_selector_out/STM32H5 series.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO96"/>
+  <dimension ref="A1:BP96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.86328125" customWidth="1" min="1" max="1"/>
@@ -575,7 +575,8 @@
     <col width="21.765625" customWidth="1" min="64" max="64"/>
     <col width="18" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
-    <col width="52" customWidth="1" min="67" max="67"/>
+    <col width="18" customWidth="1" min="67" max="67"/>
+    <col width="52" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -913,6 +914,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1010,6 +1016,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1344,6 +1351,11 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -1681,6 +1693,11 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -2018,6 +2035,11 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -2355,6 +2377,11 @@
       </c>
       <c r="BO15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h573ai.pdf</t>
         </is>
       </c>
@@ -2692,6 +2719,11 @@
       </c>
       <c r="BO16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h573ai.pdf</t>
         </is>
       </c>
@@ -3029,6 +3061,11 @@
       </c>
       <c r="BO17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -3366,6 +3403,11 @@
       </c>
       <c r="BO18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -3703,6 +3745,11 @@
       </c>
       <c r="BO19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h573ai.pdf</t>
         </is>
       </c>
@@ -4040,6 +4087,11 @@
       </c>
       <c r="BO20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -4377,6 +4429,11 @@
       </c>
       <c r="BO21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h573ai.pdf</t>
         </is>
       </c>
@@ -4714,6 +4771,11 @@
       </c>
       <c r="BO22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -5051,6 +5113,11 @@
       </c>
       <c r="BO23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h573ai.pdf</t>
         </is>
       </c>
@@ -5388,6 +5455,11 @@
       </c>
       <c r="BO24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -5725,6 +5797,11 @@
       </c>
       <c r="BO25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -6062,6 +6139,11 @@
       </c>
       <c r="BO26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h573ai.pdf</t>
         </is>
       </c>
@@ -6399,6 +6481,11 @@
       </c>
       <c r="BO27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -6736,6 +6823,11 @@
       </c>
       <c r="BO28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -7073,6 +7165,11 @@
       </c>
       <c r="BO29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -7410,6 +7507,11 @@
       </c>
       <c r="BO30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h573ai.pdf</t>
         </is>
       </c>
@@ -7747,6 +7849,11 @@
       </c>
       <c r="BO31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -8084,6 +8191,11 @@
       </c>
       <c r="BO32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -8421,6 +8533,11 @@
       </c>
       <c r="BO33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -8758,6 +8875,11 @@
       </c>
       <c r="BO34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -9095,6 +9217,11 @@
       </c>
       <c r="BO35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -9432,6 +9559,11 @@
       </c>
       <c r="BO36" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -9769,6 +9901,11 @@
       </c>
       <c r="BO37" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP37" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -10106,6 +10243,11 @@
       </c>
       <c r="BO38" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP38" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -10443,6 +10585,11 @@
       </c>
       <c r="BO39" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP39" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -10780,6 +10927,11 @@
       </c>
       <c r="BO40" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP40" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -11117,6 +11269,11 @@
       </c>
       <c r="BO41" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP41" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
@@ -11454,6 +11611,11 @@
       </c>
       <c r="BO42" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP42" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
@@ -11791,6 +11953,11 @@
       </c>
       <c r="BO43" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP43" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
@@ -12128,6 +12295,11 @@
       </c>
       <c r="BO44" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP44" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
@@ -12465,6 +12637,11 @@
       </c>
       <c r="BO45" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP45" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
@@ -12802,6 +12979,11 @@
       </c>
       <c r="BO46" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP46" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
         </is>
       </c>
@@ -13139,6 +13321,11 @@
       </c>
       <c r="BO47" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP47" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
@@ -13476,6 +13663,11 @@
       </c>
       <c r="BO48" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP48" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
         </is>
       </c>
@@ -13813,6 +14005,11 @@
       </c>
       <c r="BO49" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP49" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
         </is>
       </c>
@@ -14150,6 +14347,11 @@
       </c>
       <c r="BO50" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP50" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
@@ -14487,6 +14689,11 @@
       </c>
       <c r="BO51" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP51" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
         </is>
       </c>
@@ -14824,6 +15031,11 @@
       </c>
       <c r="BO52" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP52" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
@@ -15161,6 +15373,11 @@
       </c>
       <c r="BO53" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP53" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h503cb.pdf</t>
         </is>
       </c>
@@ -15498,6 +15715,11 @@
       </c>
       <c r="BO54" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP54" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h503cb.pdf</t>
         </is>
       </c>
@@ -15835,6 +16057,11 @@
       </c>
       <c r="BO55" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP55" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h503cb.pdf</t>
         </is>
       </c>
@@ -16172,6 +16399,11 @@
       </c>
       <c r="BO56" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP56" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h503cb.pdf</t>
         </is>
       </c>
@@ -16509,6 +16741,11 @@
       </c>
       <c r="BO57" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP57" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h553cg.pdf</t>
         </is>
       </c>
@@ -16846,6 +17083,11 @@
       </c>
       <c r="BO58" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP58" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h543ce.pdf</t>
         </is>
       </c>
@@ -17183,6 +17425,11 @@
       </c>
       <c r="BO59" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP59" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h543ce.pdf</t>
         </is>
       </c>
@@ -17520,6 +17767,11 @@
       </c>
       <c r="BO60" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP60" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h553cg.pdf</t>
         </is>
       </c>
@@ -17857,6 +18109,11 @@
       </c>
       <c r="BO61" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP61" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h543ce.pdf</t>
         </is>
       </c>
@@ -18194,6 +18451,11 @@
       </c>
       <c r="BO62" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP62" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h543ce.pdf</t>
         </is>
       </c>
@@ -18531,6 +18793,11 @@
       </c>
       <c r="BO63" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP63" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h553cg.pdf</t>
         </is>
       </c>
@@ -18868,6 +19135,11 @@
       </c>
       <c r="BO64" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP64" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h543ce.pdf</t>
         </is>
       </c>
@@ -19205,6 +19477,11 @@
       </c>
       <c r="BO65" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP65" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h543ce.pdf</t>
         </is>
       </c>
@@ -19542,6 +19819,11 @@
       </c>
       <c r="BO66" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP66" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h543ce.pdf</t>
         </is>
       </c>
@@ -19879,6 +20161,11 @@
       </c>
       <c r="BO67" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP67" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h553cg.pdf</t>
         </is>
       </c>
@@ -20216,6 +20503,11 @@
       </c>
       <c r="BO68" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP68" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h553cg.pdf</t>
         </is>
       </c>
@@ -20553,6 +20845,11 @@
       </c>
       <c r="BO69" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP69" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h543ce.pdf</t>
         </is>
       </c>
@@ -20890,6 +21187,11 @@
       </c>
       <c r="BO70" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP70" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h543ce.pdf</t>
         </is>
       </c>
@@ -21227,6 +21529,11 @@
       </c>
       <c r="BO71" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BP71" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h523cc.pdf</t>
         </is>
       </c>
@@ -21564,6 +21871,11 @@
       </c>
       <c r="BO72" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BP72" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h523cc.pdf</t>
         </is>
       </c>
@@ -21901,6 +22213,11 @@
       </c>
       <c r="BO73" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BP73" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h523cc.pdf</t>
         </is>
       </c>
@@ -22238,6 +22555,11 @@
       </c>
       <c r="BO74" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BP74" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h523cc.pdf</t>
         </is>
       </c>
@@ -22575,6 +22897,11 @@
       </c>
       <c r="BO75" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP75" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h533ce.pdf</t>
         </is>
       </c>
@@ -22912,6 +23239,11 @@
       </c>
       <c r="BO76" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BP76" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h523cc.pdf</t>
         </is>
       </c>
@@ -23249,6 +23581,11 @@
       </c>
       <c r="BO77" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP77" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h533ce.pdf</t>
         </is>
       </c>
@@ -23586,6 +23923,11 @@
       </c>
       <c r="BO78" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP78" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h533ce.pdf</t>
         </is>
       </c>
@@ -23923,6 +24265,11 @@
       </c>
       <c r="BO79" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP79" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h533ce.pdf</t>
         </is>
       </c>
@@ -24260,6 +24607,11 @@
       </c>
       <c r="BO80" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BP80" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h523cc.pdf</t>
         </is>
       </c>
@@ -24597,6 +24949,11 @@
       </c>
       <c r="BO81" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BP81" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h523cc.pdf</t>
         </is>
       </c>
@@ -24934,6 +25291,11 @@
       </c>
       <c r="BO82" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BP82" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h523cc.pdf</t>
         </is>
       </c>
@@ -25271,6 +25633,11 @@
       </c>
       <c r="BO83" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BP83" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h523cc.pdf</t>
         </is>
       </c>
@@ -25608,6 +25975,11 @@
       </c>
       <c r="BO84" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP84" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h533ce.pdf</t>
         </is>
       </c>
@@ -25945,6 +26317,11 @@
       </c>
       <c r="BO85" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP85" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
@@ -26282,6 +26659,11 @@
       </c>
       <c r="BO86" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP86" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
         </is>
       </c>
@@ -26619,6 +27001,11 @@
       </c>
       <c r="BO87" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP87" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
@@ -26956,6 +27343,11 @@
       </c>
       <c r="BO88" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP88" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
@@ -27293,6 +27685,11 @@
       </c>
       <c r="BO89" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP89" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
         </is>
       </c>
@@ -27630,6 +28027,11 @@
       </c>
       <c r="BO90" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP90" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
         </is>
       </c>
@@ -27967,6 +28369,11 @@
       </c>
       <c r="BO91" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP91" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
@@ -28304,6 +28711,11 @@
       </c>
       <c r="BO92" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP92" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
@@ -28641,6 +29053,11 @@
       </c>
       <c r="BO93" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP93" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5f4aj.pdf</t>
         </is>
       </c>
@@ -28978,6 +29395,11 @@
       </c>
       <c r="BO94" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP94" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
@@ -29315,6 +29737,11 @@
       </c>
       <c r="BO95" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP95" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
@@ -29652,12 +30079,17 @@
       </c>
       <c r="BO96" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP96" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h5e4aj.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="67">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -29680,12 +30112,14 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="A9:BP9"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -29700,9 +30134,8 @@
     <mergeCell ref="BH10:BH11"/>
     <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="A9:BO9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
@@ -29823,7 +30256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO96"/>
+  <dimension ref="A1:BP96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -29893,6 +30326,7 @@
     <col width="16" customWidth="1" min="65" max="65"/>
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
+    <col width="16" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30236,6 +30670,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -30333,6 +30772,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -30665,7 +31105,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO12" s="6" t="inlineStr">
+      <c r="BO12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31002,7 +31447,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO13" s="6" t="inlineStr">
+      <c r="BO13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31339,7 +31789,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO14" s="6" t="inlineStr">
+      <c r="BO14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31676,7 +32131,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO15" s="6" t="inlineStr">
+      <c r="BO15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32013,7 +32473,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO16" s="6" t="inlineStr">
+      <c r="BO16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32350,7 +32815,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO17" s="6" t="inlineStr">
+      <c r="BO17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32687,7 +33157,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO18" s="6" t="inlineStr">
+      <c r="BO18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33024,7 +33499,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO19" s="6" t="inlineStr">
+      <c r="BO19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33361,7 +33841,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO20" s="6" t="inlineStr">
+      <c r="BO20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33698,7 +34183,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO21" s="6" t="inlineStr">
+      <c r="BO21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34035,7 +34525,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO22" s="6" t="inlineStr">
+      <c r="BO22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34372,7 +34867,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO23" s="6" t="inlineStr">
+      <c r="BO23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34709,7 +35209,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO24" s="6" t="inlineStr">
+      <c r="BO24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35046,7 +35551,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO25" s="6" t="inlineStr">
+      <c r="BO25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35383,7 +35893,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO26" s="6" t="inlineStr">
+      <c r="BO26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35720,7 +36235,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO27" s="6" t="inlineStr">
+      <c r="BO27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36057,7 +36577,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO28" s="6" t="inlineStr">
+      <c r="BO28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36394,7 +36919,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO29" s="6" t="inlineStr">
+      <c r="BO29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36731,7 +37261,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO30" s="6" t="inlineStr">
+      <c r="BO30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37068,7 +37603,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO31" s="6" t="inlineStr">
+      <c r="BO31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37405,7 +37945,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO32" s="6" t="inlineStr">
+      <c r="BO32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37742,7 +38287,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO33" s="6" t="inlineStr">
+      <c r="BO33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38079,7 +38629,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO34" s="6" t="inlineStr">
+      <c r="BO34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38416,7 +38971,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO35" s="6" t="inlineStr">
+      <c r="BO35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38753,7 +39313,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO36" s="6" t="inlineStr">
+      <c r="BO36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39090,7 +39655,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO37" s="6" t="inlineStr">
+      <c r="BO37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP37" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39427,7 +39997,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO38" s="6" t="inlineStr">
+      <c r="BO38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP38" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39764,7 +40339,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO39" s="6" t="inlineStr">
+      <c r="BO39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP39" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40101,7 +40681,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO40" s="6" t="inlineStr">
+      <c r="BO40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP40" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40438,7 +41023,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO41" s="6" t="inlineStr">
+      <c r="BO41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP41" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40775,7 +41365,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO42" s="6" t="inlineStr">
+      <c r="BO42" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP42" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41112,7 +41707,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO43" s="6" t="inlineStr">
+      <c r="BO43" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP43" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41449,7 +42049,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO44" s="6" t="inlineStr">
+      <c r="BO44" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP44" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41786,7 +42391,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO45" s="6" t="inlineStr">
+      <c r="BO45" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP45" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42123,7 +42733,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO46" s="6" t="inlineStr">
+      <c r="BO46" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP46" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42460,7 +43075,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO47" s="6" t="inlineStr">
+      <c r="BO47" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP47" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42797,7 +43417,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO48" s="6" t="inlineStr">
+      <c r="BO48" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP48" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43134,7 +43759,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO49" s="6" t="inlineStr">
+      <c r="BO49" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP49" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43471,7 +44101,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO50" s="6" t="inlineStr">
+      <c r="BO50" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP50" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43808,7 +44443,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO51" s="6" t="inlineStr">
+      <c r="BO51" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP51" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44145,7 +44785,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO52" s="6" t="inlineStr">
+      <c r="BO52" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP52" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44482,7 +45127,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO53" s="6" t="inlineStr">
+      <c r="BO53" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP53" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44819,7 +45469,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO54" s="6" t="inlineStr">
+      <c r="BO54" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP54" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45156,7 +45811,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO55" s="6" t="inlineStr">
+      <c r="BO55" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP55" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45493,7 +46153,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO56" s="6" t="inlineStr">
+      <c r="BO56" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP56" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45830,7 +46495,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO57" s="6" t="inlineStr">
+      <c r="BO57" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP57" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46167,7 +46837,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO58" s="6" t="inlineStr">
+      <c r="BO58" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP58" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46504,7 +47179,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO59" s="6" t="inlineStr">
+      <c r="BO59" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP59" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46841,7 +47521,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO60" s="6" t="inlineStr">
+      <c r="BO60" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP60" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47178,7 +47863,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO61" s="6" t="inlineStr">
+      <c r="BO61" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP61" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47515,7 +48205,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO62" s="6" t="inlineStr">
+      <c r="BO62" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP62" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47852,7 +48547,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO63" s="6" t="inlineStr">
+      <c r="BO63" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP63" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48189,7 +48889,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO64" s="6" t="inlineStr">
+      <c r="BO64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP64" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48526,7 +49231,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO65" s="6" t="inlineStr">
+      <c r="BO65" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP65" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48863,7 +49573,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO66" s="6" t="inlineStr">
+      <c r="BO66" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP66" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49200,7 +49915,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO67" s="6" t="inlineStr">
+      <c r="BO67" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP67" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49537,7 +50257,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO68" s="6" t="inlineStr">
+      <c r="BO68" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP68" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49874,7 +50599,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO69" s="6" t="inlineStr">
+      <c r="BO69" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP69" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50211,7 +50941,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO70" s="6" t="inlineStr">
+      <c r="BO70" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP70" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50548,7 +51283,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO71" s="6" t="inlineStr">
+      <c r="BO71" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BP71" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50885,7 +51625,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO72" s="6" t="inlineStr">
+      <c r="BO72" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BP72" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -51222,7 +51967,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO73" s="6" t="inlineStr">
+      <c r="BO73" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BP73" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -51559,7 +52309,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO74" s="6" t="inlineStr">
+      <c r="BO74" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BP74" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -51896,7 +52651,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO75" s="6" t="inlineStr">
+      <c r="BO75" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP75" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52233,7 +52993,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO76" s="6" t="inlineStr">
+      <c r="BO76" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BP76" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52570,7 +53335,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO77" s="6" t="inlineStr">
+      <c r="BO77" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP77" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52907,7 +53677,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO78" s="6" t="inlineStr">
+      <c r="BO78" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP78" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53244,7 +54019,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO79" s="6" t="inlineStr">
+      <c r="BO79" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP79" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53581,7 +54361,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO80" s="6" t="inlineStr">
+      <c r="BO80" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BP80" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53918,7 +54703,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO81" s="6" t="inlineStr">
+      <c r="BO81" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BP81" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -54255,7 +55045,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO82" s="6" t="inlineStr">
+      <c r="BO82" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BP82" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -54592,7 +55387,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO83" s="6" t="inlineStr">
+      <c r="BO83" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BP83" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -54929,7 +55729,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO84" s="6" t="inlineStr">
+      <c r="BO84" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP84" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -55266,7 +56071,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO85" s="6" t="inlineStr">
+      <c r="BO85" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP85" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -55603,7 +56413,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO86" s="6" t="inlineStr">
+      <c r="BO86" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP86" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -55940,7 +56755,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO87" s="6" t="inlineStr">
+      <c r="BO87" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP87" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -56277,7 +57097,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO88" s="6" t="inlineStr">
+      <c r="BO88" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP88" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -56614,7 +57439,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO89" s="6" t="inlineStr">
+      <c r="BO89" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP89" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -56951,7 +57781,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO90" s="6" t="inlineStr">
+      <c r="BO90" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP90" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -57288,7 +58123,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO91" s="6" t="inlineStr">
+      <c r="BO91" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP91" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -57625,7 +58465,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO92" s="6" t="inlineStr">
+      <c r="BO92" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP92" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -57962,7 +58807,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO93" s="6" t="inlineStr">
+      <c r="BO93" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP93" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -58299,7 +59149,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO94" s="6" t="inlineStr">
+      <c r="BO94" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP94" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -58636,7 +59491,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO95" s="6" t="inlineStr">
+      <c r="BO95" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP95" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -58973,7 +59833,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO96" s="6" t="inlineStr">
+      <c r="BO96" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP96" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -58981,8 +59846,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BO9"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="A1:BP8"/>
+    <mergeCell ref="A9:BP9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
